--- a/AEF_template/AEF_CMA6_second_iteration.xlsx
+++ b/AEF_template/AEF_CMA6_second_iteration.xlsx
@@ -4022,9 +4022,30 @@
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
     <Ready xmlns="819ae873-75e1-413b-9d00-7af9258cf281">true</Ready>
-    <Comments xmlns="819ae873-75e1-413b-9d00-7af9258cf281" xsi:nil="true"/>
     <Doc_x002e_SymbolNumber xmlns="819ae873-75e1-413b-9d00-7af9258cf281" xsi:nil="true"/>
     <_Flow_SignoffStatus xmlns="819ae873-75e1-413b-9d00-7af9258cf281" xsi:nil="true"/>
+    <Formatter_x0028_s_x0029_ xmlns="819ae873-75e1-413b-9d00-7af9258cf281">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Formatter_x0028_s_x0029_>
+    <Status xmlns="819ae873-75e1-413b-9d00-7af9258cf281">true</Status>
+    <Teamleademail xmlns="819ae873-75e1-413b-9d00-7af9258cf281">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Teamleademail>
+    <Drafter_x0028_s_x0029_ xmlns="819ae873-75e1-413b-9d00-7af9258cf281">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Drafter_x0028_s_x0029_>
   </documentManagement>
 </p:properties>
 </file>
@@ -4035,8 +4056,8 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008FB6730B0802B54A9F00C78B857E1443" ma:contentTypeVersion="21" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3aa8ea1b9f2e27c2fdef6ef4056186e5">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="819ae873-75e1-413b-9d00-7af9258cf281" xmlns:ns3="eb4559c4-8463-4985-927f-f0d558bff8f0" xmlns:ns4="13d80b15-5f07-43ab-b435-85767a7dac08" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="16259e29b70fac56f05f7b64cc1f875d" ns2:_="" ns3:_="" ns4:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008FB6730B0802B54A9F00C78B857E1443" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9d684dda10f4f2dbf746fae76444930a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="819ae873-75e1-413b-9d00-7af9258cf281" xmlns:ns3="eb4559c4-8463-4985-927f-f0d558bff8f0" xmlns:ns4="13d80b15-5f07-43ab-b435-85767a7dac08" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2e1a7d6f560f2b9324fa8d4f4f1cd31a" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="819ae873-75e1-413b-9d00-7af9258cf281"/>
     <xsd:import namespace="eb4559c4-8463-4985-927f-f0d558bff8f0"/>
     <xsd:import namespace="13d80b15-5f07-43ab-b435-85767a7dac08"/>
@@ -4063,9 +4084,12 @@
                 <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:Comments" minOccurs="0"/>
                 <xsd:element ref="ns2:Ready" minOccurs="0"/>
                 <xsd:element ref="ns2:_Flow_SignoffStatus" minOccurs="0"/>
+                <xsd:element ref="ns2:Teamleademail" minOccurs="0"/>
+                <xsd:element ref="ns2:Drafter_x0028_s_x0029_" minOccurs="0"/>
+                <xsd:element ref="ns2:Formatter_x0028_s_x0029_" minOccurs="0"/>
+                <xsd:element ref="ns2:Status" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -4154,21 +4178,81 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="Comments" ma:index="26" nillable="true" ma:displayName="Comments" ma:format="Dropdown" ma:internalName="Comments">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Ready" ma:index="27" nillable="true" ma:displayName="Ready" ma:default="1" ma:format="Dropdown" ma:internalName="Ready">
+    <xsd:element name="Ready" ma:index="26" nillable="true" ma:displayName="Ready" ma:default="1" ma:format="Dropdown" ma:internalName="Ready">
       <xsd:simpleType>
         <xsd:restriction base="dms:Boolean"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_Flow_SignoffStatus" ma:index="28" nillable="true" ma:displayName="Sign-off status" ma:internalName="_x0024_Resources_x003a_core_x002c_Signoff_Status">
+    <xsd:element name="_Flow_SignoffStatus" ma:index="27" nillable="true" ma:displayName="Sign-off status" ma:format="Dropdown" ma:internalName="_x0024_Resources_x003a_core_x002c_Signoff_Status">
       <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
+        <xsd:restriction base="dms:Choice">
+          <xsd:enumeration value="WIP"/>
+          <xsd:enumeration value="Ready for clearance"/>
+          <xsd:enumeration value="Cleared"/>
+          <xsd:enumeration value="Returned"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Teamleademail" ma:index="28" nillable="true" ma:displayName="Team lead(s)" ma:format="Dropdown" ma:list="UserInfo" ma:SharePointGroup="0" ma:internalName="Teamleademail">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="Drafter_x0028_s_x0029_" ma:index="29" nillable="true" ma:displayName="Drafter(s)" ma:format="Dropdown" ma:list="UserInfo" ma:SharePointGroup="0" ma:internalName="Drafter_x0028_s_x0029_">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="Formatter_x0028_s_x0029_" ma:index="30" nillable="true" ma:displayName="Formatter(s)" ma:format="Dropdown" ma:list="UserInfo" ma:SharePointGroup="0" ma:internalName="Formatter_x0028_s_x0029_">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:User">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="Status" ma:index="31" nillable="true" ma:displayName="Status" ma:default="1" ma:format="Dropdown" ma:internalName="Status">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Boolean"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -4352,23 +4436,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47999317-191F-42EB-A12B-D9292F90B5CC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="819ae873-75e1-413b-9d00-7af9258cf281"/>
-    <ds:schemaRef ds:uri="eb4559c4-8463-4985-927f-f0d558bff8f0"/>
-    <ds:schemaRef ds:uri="13d80b15-5f07-43ab-b435-85767a7dac08"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB2EF094-0484-4246-825A-4ABC2F9784FE}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
